--- a/output/upload/S00026_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1984002</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>6415001</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1394,17 +1386,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>1984002</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>6415001</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1484,17 +1468,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>1984002</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>6415001</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -1574,17 +1550,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1984002</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>6415001</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -1664,17 +1632,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>1984002</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>6415001</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -1754,17 +1714,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1984002</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>6415001</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">

--- a/output/upload/S00026_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1984001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>19841</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1386,11 +1406,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1984001</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>19841</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1468,11 +1508,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1984001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>19841</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1550,11 +1610,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1984001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>19841</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1632,11 +1712,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1984001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>19841</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1714,11 +1814,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1984001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>19841</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>1984001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>1984001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>1984001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>1984001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>1984001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>1984001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">

--- a/output/upload/S00026_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1916,31 +1916,83 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
@@ -1966,31 +2018,83 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
@@ -2016,31 +2120,83 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
+      <c r="O15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
+      <c r="X15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
@@ -2066,31 +2222,83 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
+      <c r="X16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
@@ -2116,31 +2324,83 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
+      <c r="O17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
+      <c r="X17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA17" s="6" t="n"/>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
@@ -2166,31 +2426,83 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+      <c r="O18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
+      <c r="X18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
@@ -2216,31 +2528,83 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
+      <c r="O19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
+      <c r="X19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA19" s="6" t="n"/>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
@@ -2266,31 +2630,83 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
+      <c r="O20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n"/>
-      <c r="Y20" s="6" t="n"/>
-      <c r="Z20" s="6" t="n"/>
+      <c r="X20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA20" s="6" t="n"/>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
@@ -2316,31 +2732,83 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="J21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+      <c r="O21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
+      <c r="X21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA21" s="6" t="n"/>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
@@ -2366,31 +2834,83 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="J22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
+      <c r="O22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
+      <c r="X22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA22" s="6" t="n"/>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>
@@ -2414,6 +2934,2246 @@
       <c r="AU22" s="6" t="n"/>
       <c r="AV22" s="6" t="n"/>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>79</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>29</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>99</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>999</v>
+      </c>
+      <c r="P25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>99</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>999</v>
+      </c>
+      <c r="P26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>79</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>29</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>999</v>
+      </c>
+      <c r="P28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>79</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>999</v>
+      </c>
+      <c r="P29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>29</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>99</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>999</v>
+      </c>
+      <c r="P31" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>99</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>999</v>
+      </c>
+      <c r="P32" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>79</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>999</v>
+      </c>
+      <c r="P33" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>29</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>999</v>
+      </c>
+      <c r="P34" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>79</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>999</v>
+      </c>
+      <c r="P35" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>29</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>999</v>
+      </c>
+      <c r="P36" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>99</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>999</v>
+      </c>
+      <c r="P37" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>99</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>999</v>
+      </c>
+      <c r="P38" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>79</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>999</v>
+      </c>
+      <c r="P39" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>29</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>999</v>
+      </c>
+      <c r="P40" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>79</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>999</v>
+      </c>
+      <c r="P41" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>29</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>999</v>
+      </c>
+      <c r="P42" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>99</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>999</v>
+      </c>
+      <c r="P43" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>99</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>999</v>
+      </c>
+      <c r="P44" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>79</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>999</v>
+      </c>
+      <c r="P45" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>29</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>999</v>
+      </c>
+      <c r="P46" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>79</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>999</v>
+      </c>
+      <c r="P47" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>29</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>999</v>
+      </c>
+      <c r="P48" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>99</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>999</v>
+      </c>
+      <c r="P49" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>99</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>999</v>
+      </c>
+      <c r="P50" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>79</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>999</v>
+      </c>
+      <c r="P51" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>29</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>999</v>
+      </c>
+      <c r="P52" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>79</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>999</v>
+      </c>
+      <c r="P53" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>29</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>999</v>
+      </c>
+      <c r="P54" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>
